--- a/target_countries_only.xlsx
+++ b/target_countries_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,10 +429,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total USD</t>
         </is>
@@ -454,7 +464,17 @@
           <t>hello@2b-ks.com</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.2b-ks.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>38344263446, 38344666273</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>6987.6</v>
       </c>
     </row>
@@ -471,437 +491,657 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>contact@2k-trade.com, support@2k-trade.com</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+          <t>contact@2k-trade.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://2k-trade.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>48785777975, 48785777974, 48785777972, 48785777971, 48785777667</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>184451.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2L DIZAJN d.o.o. (Prestige Decor)</t>
+          <t>2K-Trade Sp. z o.o.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>prestige.decor1@hotmail.com, info@prestige-decor.info</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5168.45</v>
+          <t>support@2k-trade.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://2k-trade.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>48785777975, 48785777974, 48785777972, 48785777971, 48785777667</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>184451.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2x3 S.A.</t>
+          <t>2L DIZAJN d.o.o. (Prestige Decor)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>biuro@2x3.pl, avsolutions@2x3.pl</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>833724.0699999999</v>
+          <t>prestige.decor1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://prestige-decor.info</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>38552431447, 385915091813</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5168.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2X3 S.A.</t>
+          <t>2L DIZAJN d.o.o. (Prestige Decor)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>biuro@2x3.pl, reklamacje@2x3.pl</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>51365.41</v>
+          <t>info@prestige-decor.info</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://prestige-decor.info</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>38552431447, 385915091813</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5168.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-Plast Kft.</t>
+          <t>2x3 S.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>info@aplast.hu</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>239106.82</v>
+          <t>biuro@2x3.pl</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.2x3.pl</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>48957841100</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>833724.0699999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. Koulikidis &amp; Sons S.A.</t>
+          <t>2x3 S.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>info@koulikidis.gr, account@koulikidis.gr</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>62575.15</v>
+          <t>avsolutions@2x3.pl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.2x3.pl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>48957841100</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>833724.0699999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABC-RO LIGHTING MANUFACTURE PRODUCTION S.R.L.</t>
+          <t>2X3 S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>office@abc-ro.ro</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>65381.04</v>
+          <t>biuro@2x3.pl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.2x3.pl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>48957653848, 48957653850</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>51365.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABRA BNG RETAIL SRL</t>
+          <t>2X3 S.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vanzari@abraconstruct.ro, sesizari@abraglass.ro, office@abraglass.ro, vanzari@abraglass.ro</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1185368.18</v>
+          <t>reklamacje@2x3.pl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.2x3.pl</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>48957653848, 48957653850</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>51365.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AC GROUP GEORGIA LTD</t>
+          <t>A-Plast Kft.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>info@ac-group.ge</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10190</v>
+          <t>info@aplast.hu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://aplast.hu</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3628920920, 3614014644, 36305397708, 36202376510</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>239106.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ACARA PRAHA s.r.o.</t>
+          <t>A. Koulikidis &amp; Sons S.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>objednavky@acara.cz, bof@acara.cz, strasnice@acara.cz, acara@acara.cz, obchod@acara.cz</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>146942.94</v>
+          <t>info@koulikidis.gr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>http://koulikidis.gr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>302310785708, 302310785177</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>62575.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ACP Air Conditioning Products SRL</t>
+          <t>A. Koulikidis &amp; Sons S.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ofertare@acp.ro, gabriel.hertanu@acp.ro, alexandru.ciolan@acp.ro</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>64677.65</v>
+          <t>account@koulikidis.gr</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>http://koulikidis.gr</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>302310785708, 302310785177</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>62575.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Advanta Consulting LLC</t>
+          <t>ABC-RO LIGHTING MANUFACTURE PRODUCTION S.R.L.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TT@ADVANTACONSULTING.GE</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>85727.72</v>
+          <t>office@abc-ro.ro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://abc-ro.ro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>40728471955, 40726787787, 0468995426</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>65381.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AES LLC</t>
+          <t>ABRA BNG RETAIL SRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>careers@aes.com, katie.lau@aes.com</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>68725.89999999999</v>
+          <t>vanzari@abraconstruct.ro</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://abraconstruct.ro/, https://abraglass.ro/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>40730707707, 402729963544, 40881314732423, 40722554728, 40738841468, 40730777705, 406666666667, 40722554428</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1185368.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Air Management Systems (AMS)</t>
+          <t>ABRA BNG RETAIL SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>info@ams.com.ge, andro.q@ams.com.ge, giorgi.machitidze@gmail.com</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>7872</v>
+          <t>sesizari@abraglass.ro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://abraconstruct.ro/, https://abraglass.ro/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>40730707707, 402729963544, 40881314732423, 40722554728, 40738841468, 40730777705, 406666666667, 40722554428</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1185368.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AKAY ALUMINIUM LTD</t>
+          <t>ABRA BNG RETAIL SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>office@aksal.eu, office@aluminiumbg.com</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11972.07</v>
+          <t>office@abraglass.ro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://abraconstruct.ro/, https://abraglass.ro/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>40730707707, 402729963544, 40881314732423, 40722554728, 40738841468, 40730777705, 406666666667, 40722554428</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1185368.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alali Prime Trade Ltd</t>
+          <t>ABRA BNG RETAIL SRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>info@alali.ge</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>25696.8</v>
+          <t>vanzari@abraglass.ro</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://abraconstruct.ro/, https://abraglass.ro/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>40730707707, 402729963544, 40881314732423, 40722554728, 40738841468, 40730777705, 406666666667, 40722554428</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1185368.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alexa-Stoilov &amp; Co LTD</t>
+          <t>AC GROUP GEORGIA LTD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>alexe_da79@yahoo.com, dkyurkchiev@medfac.mu-sofia.bg</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>8786.219999999999</v>
+          <t>info@ac-group.ge</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.ac-group.ge</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>995322054262, 995322054272</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AlfaStar Systems SRL</t>
+          <t>ACARA PRAHA s.r.o.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bogdan@alfastarsystems.ro, anita@alfastarsystems.ro, office@alfastarsystems.ro</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>338888.95</v>
+          <t>objednavky@acara.cz</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.acara.cz</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>420232000888</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>146942.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALISTERM CONSTRUCT SRL</t>
+          <t>ACARA PRAHA s.r.o.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>office@terasesticla.ro, valentinceauranu@alisterm.ro, romulus.maier@alisterm.ro</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>65208.91</v>
+          <t>bof@acara.cz</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.acara.cz</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>420232000888</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>146942.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALCOM LLC</t>
+          <t>ACARA PRAHA s.r.o.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>info@alcom.ge</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>191340.78</v>
+          <t>strasnice@acara.cz</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.acara.cz</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>420232000888</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>146942.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALL-P GROUP LLC</t>
+          <t>ACARA PRAHA s.r.o.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>info@elementholding.ge</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>9131.610000000001</v>
+          <t>acara@acara.cz</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.acara.cz</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>420232000888</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>146942.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALLIMEX GREEN POWER ROMANIA SRL</t>
+          <t>ACARA PRAHA s.r.o.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>info@allimex-greenpower.eu, info.romania@allimex-greenpower.eu</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>34611.56</v>
+          <t>obchod@acara.cz</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.acara.cz</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>420232000888</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>146942.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ally Met Technology SRL</t>
+          <t>ACP Air Conditioning Products SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -911,17 +1151,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>office@allymet.ro</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>916977.79</v>
+          <t>ofertare@acp.ro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://acp.ro/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>40213503810, 40758030402, 40725681289, 40760247368</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>64677.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALLYMET TECHNOLOGY ALUMINIUM</t>
+          <t>ACP Air Conditioning Products SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -931,17 +1181,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>laura.popescu@allymet.ro, office@allymet.ro</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>166736.1</v>
+          <t>gabriel.hertanu@acp.ro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://acp.ro/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>40213503810, 40758030402, 40725681289, 40760247368</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>64677.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ALPROF SA</t>
+          <t>ACP Air Conditioning Products SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,17 +1211,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>office@alprof.ro</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>737098.02</v>
+          <t>alexandru.ciolan@acp.ro</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://acp.ro/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>40213503810, 40758030402, 40725681289, 40760247368</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>64677.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALUMET LLC</t>
+          <t>Advanta Consulting LLC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -971,77 +1241,117 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>info@alumet.ge, agobronidze@alumet.ge, purchase@alumet.ge</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>720922.36</v>
+          <t>TT@ADVANTACONSULTING.GE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://advantaconsulting.ge/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>995577755175</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>85727.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ALUMETAL AG</t>
+          <t>AES LLC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>info@alumetal.ch</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>5020.73</v>
+          <t>careers@aes.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.aes.com/contact</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>13172618261, 5072062600, 310207970700, 5712869362, 55226868900, 17035221315</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>68725.89999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ALUMETCO PROFIL SRL</t>
+          <t>AES LLC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>info@alu-metco.com</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>291658.76</v>
+          <t>katie.lau@aes.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.aes.com/contact</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>13172618261, 5072062600, 310207970700, 5712869362, 55226868900, 17035221315</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>68725.89999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ALUMIL ALUMINIUM INDUSTRY S.A.</t>
+          <t>Air Management Systems (AMS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>info@alumil.com</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>152904.71</v>
+          <t>info@ams.com.ge</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.ams.com.ge</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>995322960010, 995591450808, 995599060066</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>7872</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aluplast Glass Ltd</t>
+          <t>Air Management Systems (AMS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,177 +1361,259 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>info.de@aluplast.net</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>102428.25</v>
+          <t>andro.q@ams.com.ge</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.ams.com.ge</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>995322960010, 995591450808, 995599060066</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>7872</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALUPROFIL LTD</t>
+          <t>Air Management Systems (AMS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>info@aluprofil.systems</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1505627.74</v>
+          <t>giorgi.machitidze@gmail.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.ams.com.ge</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>995322960010, 995591450808, 995599060066</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>7872</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALUSEL SYSTEMS S.R.L.</t>
+          <t>AKAY ALUMINIUM LTD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ofertare@kondorinvest.ro, comenzi@kondorinvest.ro, office@kondorinvest.ro, parteneri@kondorinvest.ro</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>413098.76</v>
+          <t>office@aksal.eu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://aksal.eu</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>359899194524, 359888396785</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>11972.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALUTERN s.r.o.</t>
+          <t>AKAY ALUMINIUM LTD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>info@alutern.cz</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>13091158.27</v>
+          <t>office@aluminiumbg.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://aksal.eu</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>359899194524, 359888396785</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>11972.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMARI ROMANIA S.R.L.</t>
+          <t>Alali Prime Trade Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>office@amari.ro, aluminiu1@amari.ro, marcela.micle@amari.ro, andrei.popa@amari.ro, aluminiu@amari.ro, bucuresti@amari.ro, tiberiu.guias@amari.ro, dragos.georgescu@amari.ro, simion.cojman@amari.ro, judit.voda@amari.ro, calin.sebesan@amari.ro</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>23094.15</v>
+          <t>info@alali.ge</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.alali.ge</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>995588887272</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>25696.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Art Foundation Anagi</t>
+          <t>Alexa-Stoilov &amp; Co LTD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>info@artfoundationanagi.com, info@artfoundationanagi.ge</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>36184.96</v>
+          <t>alexe_da79@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>35970080031</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>8786.219999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ANY-COM TRANS S.R.L.</t>
+          <t>Alexa-Stoilov &amp; Co LTD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>office@anycomtrans.com, blikero92@gmail.com</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>33466.82</v>
+          <t>dkyurkchiev@medfac.mu-sofia.bg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>35970080031</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>8786.219999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Apline Europe Bulgaria</t>
+          <t>AlfaStar Systems SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>apline@apline.bg</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10449.86</v>
+          <t>bogdan@alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>40749214982, 40746278089</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>338888.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aqua Promet D.O.O.</t>
+          <t>AlfaStar Systems SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>office@aquapromet.com, servis@aquapromet.com, prodaja2@aquapromet.com, prodaja3@aquapromet.com, maloprodaja1@aquapromet.com, maloprodaja4@aquapromet.com, komercijalavp2@aquapromet.com, nenad.vuckovic@aquapromet.com, veleprodajabgd1@aquapromet.com, racunovodstvo@aquapromet.com</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11363</v>
+          <t>anita@alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>40749214982, 40746278089</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>338888.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Arabesque SRL</t>
+          <t>AlfaStar Systems SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,57 +1623,87 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>office@arabesque.ro</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>356302.24</v>
+          <t>office@alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://alfastarsystems.ro</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>40749214982, 40746278089</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>338888.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Archtrade LLC</t>
+          <t>ALISTERM CONSTRUCT SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>info@archtrade.ge</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11833.5</v>
+          <t>office@terasesticla.ro</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.terasesticla.ro/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>40753157297, 40711960573, 40711954246</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>65208.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Arena Glass Group Ltd.</t>
+          <t>ALISTERM CONSTRUCT SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>info@arenaglassgroup.com</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>14284.84</v>
+          <t>valentinceauranu@alisterm.ro</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.terasesticla.ro/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40753157297, 40711960573, 40711954246</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>65208.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ARFEN EUROPE S.R.L.</t>
+          <t>ALISTERM CONSTRUCT SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1291,37 +1713,57 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sales1@arfen.eu, contact@arfen.eu, cristi.pana@arfen.eu</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>34246.15</v>
+          <t>romulus.maier@alisterm.ro</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.terasesticla.ro/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40753157297, 40711960573, 40711954246</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>65208.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARH CITYSTROY LTD EOOD</t>
+          <t>ALCOM LLC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>office@arhcitystroy.com, d.kircheva@arhcitystroy.com, pto@arhcitystroy.com, dkamburova.pto@arhcitystroy.com, shtarbanova@arhcitystroy.com, bratanov@arhcitystroy.com, stoyanov@arhcitystroy.com, trifonov@arhcitystroy.com, dimitrov@arhcitystroy.com, karamuzova@arhcitystroy.com</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>46904.3</v>
+          <t>info@alcom.ge</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://alcom.ge</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>995322110072, 995599198382</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>191340.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Artwin Georgia LLC</t>
+          <t>ALL-P GROUP LLC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1331,37 +1773,57 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>info@artwin.ge</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>5472.85</v>
+          <t>info@elementholding.ge</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://elementholding.ge</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>995322374737</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9131.610000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARTISTICO-SYSTEMS OOD</t>
+          <t>ALLIMEX GREEN POWER ROMANIA SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>office@artistico-systems.bg</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>7668</v>
+          <t>info@allimex-greenpower.eu</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://allimexgreenpower.com/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40725922982, 40749161666, 3211460070</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>34611.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARYA DESIGN INTERNATIONAL SRL</t>
+          <t>ALLIMEX GREEN POWER ROMANIA SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,37 +1833,57 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>vanzari@aryadesign.ro, office@aryadesign.ro</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>33882.06</v>
+          <t>info.romania@allimex-greenpower.eu</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://allimexgreenpower.com/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>40725922982, 40749161666, 3211460070</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>34611.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASISTAL ALUMINIUM LTD</t>
+          <t>Ally Met Technology SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>office@asistal.bg, export@asistal.com</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>864351.91</v>
+          <t>office@allymet.ro</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.profil-aluminiu.ro/, https://www.allymet.ro/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>40721404964, 40726200663, 40213611000</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>916977.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SC Atlas Concept SRL</t>
+          <t>ALLYMET TECHNOLOGY ALUMINIUM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1411,97 +1893,147 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>office@atlasconcept.eu</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>12249.35</v>
+          <t>laura.popescu@allymet.ro</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.profil-aluminiu.ro/, https://www.allymet.ro/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>40726200663, 40725540472, 40724363003, 40728914525</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>166736.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Audax Corp Ltd</t>
+          <t>ALLYMET TECHNOLOGY ALUMINIUM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>account@audax-corp.com, office@audax-corp.com, trade@audax-corp.com</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4341406.36</v>
+          <t>office@allymet.ro</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.profil-aluminiu.ro/, https://www.allymet.ro/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>40726200663, 40725540472, 40724363003, 40728914525</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>166736.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Austa LTD</t>
+          <t>ALPROF SA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>austa@abv.bg, austa@mbox.digsys.bg</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>6692.2</v>
+          <t>office@alprof.ro</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.alprof.ro</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>40241255696, 40241255336, 40241225696</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>737098.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Balkan Yug OOD</t>
+          <t>ALUMET LLC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>balkanyug@abv.bg</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>446994.97</v>
+          <t>info@alumet.ge</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://alumet.ge</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>995595333339, 995577141173</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>720922.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Baros Vision EOOD</t>
+          <t>ALUMET LLC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>office@barosvision.com, Sales@barosvision.com</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>5123581.29</v>
+          <t>agobronidze@alumet.ge</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://alumet.ge</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>995595333339, 995577141173</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>720922.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BARS MEKATRONIK LTD</t>
+          <t>ALUMET LLC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1511,17 +2043,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>office@bars.ge</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10815.03</v>
+          <t>purchase@alumet.ge</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://alumet.ge</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>995595333339, 995577141173</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>720922.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BAUINDUSTRY DC SRL</t>
+          <t>ALUMETAL AG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1531,17 +2073,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bauindustrydc@gmail.com, bauindustry.dc@gmail.com</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>25084.18</v>
+          <t>info@alumetal.ch</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://alumetal.ch/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>41916954020, 41916954021</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5020.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BBB INVEST SRL</t>
+          <t>ALUMETCO PROFIL SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,97 +2103,143 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>office@bbbinvest.ro</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>150681.07</v>
+          <t>info@alu-metco.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.alu-metco.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40757121315</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>291658.76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Beta Global Ltd.</t>
+          <t>ALUMIL ALUMINIUM INDUSTRY S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>betagl@abv.bg</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1834202.14</v>
+          <t>info@alumil.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.alumil.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>302341079300, 302313011000, 302108003700, 302541087334</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>152904.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BG PLAST 1 EOOD</t>
+          <t>Aluplast Glass Ltd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>office@bg-plast.com, sales@bg-plast.com, julian.bandrov@bg-plast.com, dani.chankova@bg-plast.com, kristina.kalpazanova@bg-plast.com</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>3439333.28</v>
+          <t>info.de@aluplast.net</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>995593708080</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>102428.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BMAX SRL</t>
+          <t>ALUPROFIL LTD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vanzari@bmax.ro, contact@bmax.ro, comercial@bmax.ro</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>97109.44</v>
+          <t>info@aluprofil.systems</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.aluprofil.systems</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>359897912505</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1505627.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BOTEK LTD</t>
+          <t>ALUSEL SYSTEMS S.R.L.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>bayko@botech-bg.com</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>71029.35000000001</v>
+          <t>ofertare@kondorinvest.ro</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://comenzi.alusel.ro/site/contact, https://www.kondorinvest.ro/contact/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40243256242, 40213378282, 40757082716, 40372508250, 40372508278, 40372508251, 40372508260</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>413098.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brillance Design SRL</t>
+          <t>ALUSEL SYSTEMS S.R.L.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1651,97 +2249,147 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>contact@brillancedesign.ro</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11592.75</v>
+          <t>comenzi@kondorinvest.ro</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://comenzi.alusel.ro/site/contact, https://www.kondorinvest.ro/contact/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40243256242, 40213378282, 40757082716, 40372508250, 40372508278, 40372508251, 40372508260</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>413098.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BTL Industries JSC</t>
+          <t>ALUSEL SYSTEMS S.R.L.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>info@btl.bg</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>61301.35</v>
+          <t>office@kondorinvest.ro</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://comenzi.alusel.ro/site/contact, https://www.kondorinvest.ro/contact/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40243256242, 40213378282, 40757082716, 40372508250, 40372508278, 40372508251, 40372508260</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>413098.76</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BTS ALUMINIUM BULGARIA LTD</t>
+          <t>ALUSEL SYSTEMS S.R.L.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>office@aluminiumbg.com, info@btsaluminium.com</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>65350.51</v>
+          <t>parteneri@kondorinvest.ro</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://comenzi.alusel.ro/site/contact, https://www.kondorinvest.ro/contact/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40243256242, 40213378282, 40757082716, 40372508250, 40372508278, 40372508251, 40372508260</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>413098.76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bus Motor Design SRL</t>
+          <t>ALUTERN s.r.o.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>office@busdesign.ro</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>14384.88</v>
+          <t>info@alutern.cz</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://alutern.cz/en/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>420739376058</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>13091158.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Consulting Georgia</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>info@bia.ge, sales@bia.ge</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>5240</v>
+          <t>office@amari.ro</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BILGIN TEXTIL S.R.L.</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1751,57 +2399,87 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>emre@3bkumas.com</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>8025.21</v>
+          <t>aluminiu1@amari.ro</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cambro Ozay BG Ltd</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kozbek@cambro.com.tr, kozbek@cambro.com, aibrahim@cambro.bg</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>24168.74</v>
+          <t>marcela.micle@amari.ro</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Caproni JSC</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>caproni@caproni.bg, nenova@caproni.bg, y.petrov@caproni.bg, m.ilieva@caproni.bg, b.draganov@caproni.bg, skatsarova@caproni.bg, r.petrova@caproni.bg, m.mircheva@caproni.bg, t.zlatova@caproni.bg, mtc@caproni.bg</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1320061.53</v>
+          <t>andrei.popa@amari.ro</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Casa Noastra S.R.L.</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1811,17 +2489,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>office@casanoastra.ro</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>25555.87</v>
+          <t>aluminiu@amari.ro</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CEM BUS CONFORT S.R.L.</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1831,57 +2519,87 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vanzari@ceminibus.ro, office@ceminibus.ro</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>18340.02</v>
+          <t>bucuresti@amari.ro</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cold Tech Ltd</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sales@coldtechshop.com, coldtechltd@gmail.com</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>5598.72</v>
+          <t>tiberiu.guias@amari.ro</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Doremi</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>117@doremi.ge, info@doremi.ge</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>76047.02</v>
+          <t>dragos.georgescu@amari.ro</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Comfortex Energy S.R.L.</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1891,37 +2609,57 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>contact@comfortex-energy.ro</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1695690.2</v>
+          <t>simion.cojman@amari.ro</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Componere Ltd</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>office@componerebg.com, development@componerebg.com</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>256813.64</v>
+          <t>judit.voda@amari.ro</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COMTEC 2000 INC SRL</t>
+          <t>AMARI ROMANIA S.R.L.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1931,57 +2669,87 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>magazin.1@comtec-int.ro, sales@comtec-int.ro, ofertare@comtec-int.ro</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>86435.72</v>
+          <t>calin.sebesan@amari.ro</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://amari.ro</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>40359173206, 40723792544, 40359173214, 40784259220, 40359173207, 40771682928, 40359173216, 40760078887, 40359173204, 40726749502</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>23094.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CONFORMA EOOD</t>
+          <t>Art Foundation Anagi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>office@conforma.bg, daniela.ivanova@conforma.bg, ivaylo.zahariev@conforma.bg, igoranov@conforma.bg, rositsa.varadinova@conforma.bg, polina.stoeva@conforma.bg, nedelina.dencheva@conforma.bg</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>74257.2</v>
+          <t>info@artfoundationanagi.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://artfoundationanagi.com/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>995322299029</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>36184.96</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CSI INDUSTRIES BV</t>
+          <t>Art Foundation Anagi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>office@csiromania.ro, info.CSi@Mpac-Group.com</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>24926.4</v>
+          <t>info@artfoundationanagi.ge</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://artfoundationanagi.com/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>995322299029</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>36184.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cuprolli Manufacturing SRL</t>
+          <t>ANY-COM TRANS S.R.L.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1991,37 +2759,57 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>office@cuprolli.ro, dorel.bujor@cuprolli.ro, corina.stetco@cuprolli.ro, alexandru.pietrariu@i-struct.ro, sebastian.petculescu@cuprolli.ro, sebastian.petculescu@i-struct.ro, ani.surugiu@cuprolli.ro</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>106198.58</v>
+          <t>office@anycomtrans.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>http://anycomtrans.com/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>40241552828, 40752137814, 40863759924</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>33466.82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D&amp;D TEXTILE OOD</t>
+          <t>ANY-COM TRANS S.R.L.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>dd@ddinternational.bg, office@ddinternational.bg, d_dtextile@abv.bg</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11197.44</v>
+          <t>blikero92@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>http://anycomtrans.com/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>40241552828, 40752137814, 40863759924</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>33466.82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DAGIO LTD EOOD</t>
+          <t>Apline Europe Bulgaria</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2031,317 +2819,473 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sales@djia.bg, onlineshop@djia.bg</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>266665.33</v>
+          <t>apline@apline.bg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://apline.bg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>10449.86</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DAROS BG LTD</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>darosbg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>151858.23</v>
+          <t>office@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Decada EOOD</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>office@decada-bg.com</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>20010.83</v>
+          <t>servis@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DECEUNINCK ROMANIA SRL</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ovidiu.cilibiu@deceuninck.com, officedeceuninck.ro@deceuninck.com</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>77945.84</v>
+          <t>prodaja2@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DECOR INOX SRL</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>office@decor-inox.ro</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>9940.18</v>
+          <t>prodaja3@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DECOR-A LTD</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>office@decora.ws, office@decor-a.bg</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>7312.8</v>
+          <t>maloprodaja1@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DELTA BG LTD</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>sales@delta.bg, support@delta.bg, export@delta-transport.eu, import@delta-transport.eu</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>16328.11</v>
+          <t>maloprodaja4@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dialust 2000 Impex SRL</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>office@dialust.ro</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>120022.15</v>
+          <t>komercijalavp2@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DIKAM-D LTD</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>office@dikam.com, dikam-d@mail.bg</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>24990.44</v>
+          <t>nenad.vuckovic@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DIO Ltd</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>info@dio.ge</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>190905.21</v>
+          <t>veleprodajabgd1@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DNS'S PANEL SRL</t>
+          <t>Aqua Promet D.O.O.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>info@dnsspanel.eu</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>875179.55</v>
+          <t>racunovodstvo@aquapromet.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.aquapromet.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>38135243809, 38135244497, 381603243826, 381603243820, 381603243839, 381114236475</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>11363</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DOM HARMONIA LTD</t>
+          <t>Arabesque SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>office@domharmonia.bg</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>17904.97</v>
+          <t>office@arabesque.ro</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://arabesque.ro</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>40236463063</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>356302.24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DORMAKABA BULGARIA EOOD</t>
+          <t>Archtrade LLC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>office.bg@dormakaba.com</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>661825.9300000001</v>
+          <t>info@archtrade.ge</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://archtrade.ge/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>995322207400, 995322207401, 995322207500</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>11833.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Doğuş Construction and Trade Inc.</t>
+          <t>Arena Glass Group Ltd.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>romania@dogusinsaat.com.tr</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>8421.67</v>
+          <t>info@arenaglassgroup.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.arenaglassgroup.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>359879531533</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>14284.84</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DS Group</t>
+          <t>ARFEN EUROPE S.R.L.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>info@dsg.ge</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>71434.07000000001</v>
+          <t>sales1@arfen.eu</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.arfen.eu</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>40785266144, 40775312056</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>34246.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>INTERNATIONAL ALM &amp; PVC CENTER OOD</t>
+          <t>ARFEN EUROPE S.R.L.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>iapcbg@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>173584.17</v>
+          <t>contact@arfen.eu</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.arfen.eu</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>40785266144, 40775312056</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>34246.15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DUNCA CONSTRUCT SRL</t>
+          <t>ARFEN EUROPE S.R.L.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2351,17 +3295,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>office@duncagroup.ro</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>27533.91</v>
+          <t>cristi.pana@arfen.eu</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.arfen.eu</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>40785266144, 40775312056</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>34246.15</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EAS Aluminium LTD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2371,17 +3325,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sales@easaluminium.eu</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>7642687.05</v>
+          <t>office@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Easydoor LTD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2391,57 +3355,87 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>import@easydoor.bg, easydoor@easydoor.bg, a.pishmanov@easydoor.com, a.pishmanov@easydoor.bg, office@easydoor.bg</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>21768.18</v>
+          <t>d.kircheva@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ECOGROUP TRANS LTD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>lctransgeorgia@gmail.com</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>38789.71</v>
+          <t>pto@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EKSEN TECHNIC SRL</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>office@eksentechnic.ro</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>19681.83</v>
+          <t>dkamburova.pto@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EL-LOGISTIC LTD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2451,17 +3445,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>lt_logistic@abv.bg, service@nbd.ltd, consultingltd@abv.bg</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>7233.75</v>
+          <t>shtarbanova@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ELAZ EOOD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2471,37 +3475,57 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>elazeood@abv.bg</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>35145.7</v>
+          <t>bratanov@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Element Construction LLC</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>info@ec.ge</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10667.97</v>
+          <t>stoyanov@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ELME - EKS - MESUT MUSTAFA ET</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2511,17 +3535,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>info@elmeex.com, elmeex@abv.bg, elmeexplv@abv.bg</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>62051.59</v>
+          <t>trifonov@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EMIR LTD</t>
+          <t>ARH CITYSTROY LTD EOOD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2531,30 +3565,3948 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>info@emir.bg, office@emir.bg, marketing.sales@emir.bg, market.manager@emir.bg, account.dept@emir.bg, magazin1@emir.bg, emir.speditor@emir.bg, mehanik@emir.bg</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>32485.58</v>
+          <t>dimitrov@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>46904.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>ARH CITYSTROY LTD EOOD</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>karamuzova@arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://arhcitystroy.com</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>359882300149, 359882300108, 359889300165, 359889300186, 359876300814, 359882300143, 359894519690, 359887092770, 359882300104, 359343685782</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>46904.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Artwin Georgia LLC</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>info@artwin.ge</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://artwin.ge</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>995322240901, 995577129980</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>5472.85</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ARTISTICO-SYSTEMS OOD</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>office@artistico-systems.bg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>http://artistico-systems.bg</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>359888400277, 35932260000, 359885077211</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>7668</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ARYA DESIGN INTERNATIONAL SRL</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>vanzari@aryadesign.ro</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>http://aryadesign.ro</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>40731227522, 40726792854, 400314251350</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>33882.06</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ARYA DESIGN INTERNATIONAL SRL</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>office@aryadesign.ro</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>http://aryadesign.ro</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>40731227522, 40726792854, 400314251350</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>33882.06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ASISTAL ALUMINIUM LTD</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>office@asistal.bg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://asistal.com/bg</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>35924440062, 359889170062</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>864351.91</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ASISTAL ALUMINIUM LTD</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>export@asistal.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://asistal.com/bg</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>35924440062, 359889170062</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>864351.91</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SC Atlas Concept SRL</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>office@atlasconcept.eu</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://atlasconcept.eu</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>40774017273, 4003130975458623, 40212707519531, 400313397726234, 400008180305391</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>12249.35</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Audax Corp Ltd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>account@audax-corp.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://audax-corp.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>35932278900, 35932278952, 35932278955, 359888411766</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>4341406.36</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Audax Corp Ltd</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>office@audax-corp.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://audax-corp.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>35932278900, 35932278952, 35932278955, 359888411766</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>4341406.36</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Audax Corp Ltd</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>trade@audax-corp.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://audax-corp.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>35932278900, 35932278952, 35932278955, 359888411766</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>4341406.36</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Austa LTD</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>austa@abv.bg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://austa-bg.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>35936165880, 35936165882, 35924522940, 35929516866</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>6692.2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Austa LTD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>austa@mbox.digsys.bg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://austa-bg.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>35936165880, 35936165882, 35924522940, 35929516866</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>6692.2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Balkan Yug OOD</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>balkanyug@abv.bg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://balkanyug.bg</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>359878925055, 359879606199</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>446994.97</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Baros Vision EOOD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>office@barosvision.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://barosvision.com/en/</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>359878145477, 359879643465, 3598760808, 3598771449</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>5123581.29</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Baros Vision EOOD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sales@barosvision.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://barosvision.com/en/</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>359878145477, 359879643465, 3598760808, 3598771449</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>5123581.29</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BARS MEKATRONIK LTD</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>office@bars.ge</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://bars.ge/en/home-page/</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>995577417600, 995577415136, 995322709181, 995577454087</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>10815.03</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BAUINDUSTRY DC SRL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bauindustrydc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.platformadeconstructii.ro</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>40727345670</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>25084.18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BAUINDUSTRY DC SRL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>bauindustry.dc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.platformadeconstructii.ro</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>40727345670</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>25084.18</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BBB INVEST SRL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>office@bbbinvest.ro</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://bbbinvest.ro/</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>40733307300, 017068463105</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>150681.07</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Beta Global Ltd.</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>betagl@abv.bg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.betaglobal.eu/</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>359898672654, 359326705611, 359363469475, 359485695155</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1834202.14</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BG PLAST 1 EOOD</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>office@bg-plast.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://bg-plast.com/</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>35929732859, 35929963188, 35929798068, 359886609566, 359896771221, 359895756159, 359878951561, 359878951562</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>3439333.28</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BG PLAST 1 EOOD</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sales@bg-plast.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://bg-plast.com/</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>35929732859, 35929963188, 35929798068, 359886609566, 359896771221, 359895756159, 359878951561, 359878951562</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>3439333.28</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>BG PLAST 1 EOOD</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>julian.bandrov@bg-plast.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://bg-plast.com/</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>35929732859, 35929963188, 35929798068, 359886609566, 359896771221, 359895756159, 359878951561, 359878951562</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>3439333.28</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BG PLAST 1 EOOD</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>dani.chankova@bg-plast.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://bg-plast.com/</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>35929732859, 35929963188, 35929798068, 359886609566, 359896771221, 359895756159, 359878951561, 359878951562</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>3439333.28</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BG PLAST 1 EOOD</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>kristina.kalpazanova@bg-plast.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://bg-plast.com/</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>35929732859, 35929963188, 35929798068, 359886609566, 359896771221, 359895756159, 359878951561, 359878951562</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>3439333.28</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BMAX SRL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>vanzari@bmax.ro</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.bmax.ro/</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>40743519916, 40741991111</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>97109.44</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BMAX SRL</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>contact@bmax.ro</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.bmax.ro/</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>40743519916, 40741991111</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>97109.44</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BMAX SRL</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>comercial@bmax.ro</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.bmax.ro/</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>40743519916, 40741991111</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>97109.44</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BOTEK LTD</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>bayko@botech-bg.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>35932630981, 35932653317</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>71029.35000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Brillance Design SRL</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>contact@brillancedesign.ro</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.brillancedesign.ro/</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0768746347, 0887645312698, 0818064242, 0818060658</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>11592.75</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BTL Industries JSC</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>info@btl.bg</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.btl.bg/</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>35932622252, 8170986080, 17954448112, 1596190871, 580285449</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>61301.35</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BTS ALUMINIUM BULGARIA LTD</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>office@aluminiumbg.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://en.aluminiumbg.com, https://www.btsaluminium.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>359888396785, 0620353113, 0387795340770, 072150469899, 0560969899</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>65350.51</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BTS ALUMINIUM BULGARIA LTD</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>info@btsaluminium.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://en.aluminiumbg.com, https://www.btsaluminium.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>359888396785, 0620353113, 0387795340770, 072150469899, 0560969899</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>65350.51</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Bus Motor Design SRL</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>office@busdesign.ro</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://busdesign.ro</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>40744637816, 40733931383</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>14384.88</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Business Consulting Georgia</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>info@bia.ge</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.bia.ge/Company/100956</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>5646449730</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Business Consulting Georgia</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sales@bia.ge</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.bia.ge/Company/100956</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>5646449730</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BILGIN TEXTIL S.R.L.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>emre@3bkumas.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>40749115802, 40212020900</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>8025.21</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Cambro Ozay BG Ltd</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>kozbek@cambro.com.tr</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.cambro.com/</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>359894091891, 022510366629, 0011294456685</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>24168.74</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cambro Ozay BG Ltd</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>kozbek@cambro.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.cambro.com/</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>359894091891, 022510366629, 0011294456685</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>24168.74</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cambro Ozay BG Ltd</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>aibrahim@cambro.bg</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.cambro.com/</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>359894091891, 022510366629, 0011294456685</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>24168.74</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>caproni@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>nenova@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>y.petrov@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>m.ilieva@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>b.draganov@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>skatsarova@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>r.petrova@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>m.mircheva@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>t.zlatova@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Caproni JSC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>mtc@caproni.bg</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.caproni.bg</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>35943162230, 35943162603, 35943163134, 35943163364, 35943163638, 35943164385, 35943162740, 35943163670, 35943164707, 35943163771, 35943163362, 35943162808, 35943162227, 35943164692</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>1320061.53</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Casa Noastra S.R.L.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>office@casanoastra.ro</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://casanoastra.ro</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>40251429532, 40251429533, 40251459115</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>25555.87</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CEM BUS CONFORT S.R.L.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>vanzari@ceminibus.ro</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://cembusconfort.ro/</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>40746269699, 40746269697, 40746266111</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>18340.02</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CEM BUS CONFORT S.R.L.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>office@ceminibus.ro</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://cembusconfort.ro/</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>40746269699, 40746269697, 40746266111</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>18340.02</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cold Tech Ltd</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sales@coldtechshop.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://coldtechshop.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>359886261631, 359898377157</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>5598.72</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Cold Tech Ltd</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>coldtechltd@gmail.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://coldtechshop.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>359886261631, 359898377157</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>5598.72</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Doremi</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>117@doremi.ge</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.doremi.ge/</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>995577333777, 995596858885</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>76047.02</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Doremi</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>info@doremi.ge</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.doremi.ge/</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>995577333777, 995596858885</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>76047.02</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Comfortex Energy S.R.L.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>contact@comfortex-energy.ro</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://comfortex-energy.ro/</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>40729868686, 40726868686</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>1695690.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Componere Ltd</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>office@componerebg.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://componerebg.com/</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>359886445114, 359886150189, 359888710684</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>256813.64</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Componere Ltd</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>development@componerebg.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://componerebg.com/</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>359886445114, 359886150189, 359888710684</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>256813.64</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>COMTEC 2000 INC SRL</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>magazin.1@comtec-int.ro</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.comtec-int.ro/</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>40213019600</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>86435.72</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>COMTEC 2000 INC SRL</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sales@comtec-int.ro</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.comtec-int.ro/</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>40213019600</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>86435.72</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>COMTEC 2000 INC SRL</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ofertare@comtec-int.ro</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.comtec-int.ro/</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>40213019600</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>86435.72</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>office@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>daniela.ivanova@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ivaylo.zahariev@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>igoranov@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>rositsa.varadinova@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>polina.stoeva@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CONFORMA EOOD</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>nedelina.dencheva@conforma.bg</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://conforma.bg/</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>359887704350, 359882806595, 359884271503, 359882214607, 359885808475, 359897898889</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>74257.2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CSI INDUSTRIES BV</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>office@csiromania.ro</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://csiromania.ro/, https://www.csiportal.com/</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>40770343329, 40213178829, 40213178828, 31162575000</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>24926.4</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CSI INDUSTRIES BV</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>info.CSi@Mpac-Group.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://csiromania.ro/, https://www.csiportal.com/</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>40770343329, 40213178829, 40213178828, 31162575000</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>24926.4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>office@cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>dorel.bujor@cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>corina.stetco@cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>alexandru.pietrariu@i-struct.ro</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sebastian.petculescu@cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>sebastian.petculescu@i-struct.ro</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Cuprolli Manufacturing SRL</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ani.surugiu@cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://cuprolli.ro</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>40740209262, 40741133389, 40749245548, 40724083039, 40754074449, 40741263240</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>106198.58</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>D&amp;D TEXTILE OOD</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>dd@ddinternational.bg</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>http://www.ddinternational.bg</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>359886568668, 359888806848, 35932968984, 359878649528</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>11197.44</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>D&amp;D TEXTILE OOD</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>office@ddinternational.bg</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>http://www.ddinternational.bg</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>359886568668, 359888806848, 35932968984, 359878649528</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>11197.44</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>D&amp;D TEXTILE OOD</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>d_dtextile@abv.bg</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>http://www.ddinternational.bg</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>359886568668, 359888806848, 35932968984, 359878649528</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>11197.44</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DAGIO LTD EOOD</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sales@djia.bg</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://djia.bg</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>35924020400, 359882947793, 359888179717</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>266665.33</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DAGIO LTD EOOD</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>onlineshop@djia.bg</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://djia.bg</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>35924020400, 359882947793, 359888179717</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>266665.33</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>DAROS BG LTD</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>darosbg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://darosbg.com</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>359878760033, 359897917799</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>151858.23</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Decada EOOD</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>office@decada-bg.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://www.decada.bg/</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>359888433487, 359896878282</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>20010.83</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DECEUNINCK ROMANIA SRL</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ovidiu.cilibiu@deceuninck.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://deceuninck.ro</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>40740090646, 40213235290, 40213274952</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>77945.84</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DECEUNINCK ROMANIA SRL</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>officedeceuninck.ro@deceuninck.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://deceuninck.ro</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>40740090646, 40213235290, 40213274952</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>77945.84</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DECOR INOX SRL</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>office@decor-inox.ro</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://www.decor-inox.ro</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>40784267901, 40741683718, 06483030319</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>9940.18</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DECOR-A LTD</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>office@decora.ws</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://decor-a.bg/</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>35929559029, 35929556277, 359435495377, 359894301405, 35982519257</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>7312.8</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DECOR-A LTD</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>office@decor-a.bg</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://decor-a.bg/</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>35929559029, 35929556277, 359435495377, 359894301405, 35982519257</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>7312.8</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DELTA BG LTD</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sales@delta.bg</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://delta.bg/en/contacts</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>35924484165, 359399971677, 359112920150662, 35914272958087</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>16328.11</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DELTA BG LTD</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>support@delta.bg</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://delta.bg/en/contacts</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>35924484165, 359399971677, 359112920150662, 35914272958087</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>16328.11</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DELTA BG LTD</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>export@delta-transport.eu</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://delta.bg/en/contacts</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>35924484165, 359399971677, 359112920150662, 35914272958087</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>16328.11</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DELTA BG LTD</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>import@delta-transport.eu</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://delta.bg/en/contacts</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>35924484165, 359399971677, 359112920150662, 35914272958087</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>16328.11</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Dialust 2000 Impex SRL</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>office@dialust.ro</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://dialust.ro</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>40724244040, 0213510002</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>120022.15</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DIKAM-D LTD</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>office@dikam.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://dikam.com/</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>359895544006, 359892264386</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>24990.44</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DIKAM-D LTD</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>dikam-d@mail.bg</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://dikam.com/</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>359895544006, 359892264386</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>24990.44</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DIO Ltd</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>info@dio.ge</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://dio.ge</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>995322361112, 995322331199</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>190905.21</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DNS'S PANEL SRL</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>info@dnsspanel.eu</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://dnsspanel.eu</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>40727043363, 40786581175</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>875179.55</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DOM HARMONIA LTD</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>office@domharmonia.bg</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://domharmonia.bg/</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>359884084725, 359884272299, 359877377686, 359887878378, 359888135902, 359888377686, 359884084726, 359888801633</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>17904.97</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DORMAKABA BULGARIA EOOD</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>office.bg@dormakaba.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://www.dormakaba.com/bg-bg/форма-за-контакт</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>35929714904</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>661825.9300000001</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Doğuş Construction and Trade Inc.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>romania@dogusinsaat.com.tr</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://www.dogusinsaat.com.tr</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>40364861000</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>8421.67</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DS Group</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>info@dsg.ge</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://dsg.ge</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>995596991111, 995596771111, 995596701111, 995596551111, 995596881111</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>71434.07000000001</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL ALM &amp; PVC CENTER OOD</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>iapcbg@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>359884950041, 35932632626</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>173584.17</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DUNCA CONSTRUCT SRL</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>office@duncagroup.ro</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://www.dunca.ro</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>40754055216, 40744368461</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>27533.91</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>EAS Aluminium LTD</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sales@easaluminium.eu</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://www.easaluminium.eu</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>359884457908, 359889224081</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7642687.05</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Easydoor LTD</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>import@easydoor.bg</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://easydoor.bg/</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>359896677878, 359896774565, 359885853333, 359889941610, 359885224330, 359889006776, 359885845750, 35934837662894</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>21768.18</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Easydoor LTD</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>easydoor@easydoor.bg</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://easydoor.bg/</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>359896677878, 359896774565, 359885853333, 359889941610, 359885224330, 359889006776, 359885845750, 35934837662894</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>21768.18</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Easydoor LTD</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>a.pishmanov@easydoor.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://easydoor.bg/</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>359896677878, 359896774565, 359885853333, 359889941610, 359885224330, 359889006776, 359885845750, 35934837662894</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>21768.18</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Easydoor LTD</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>a.pishmanov@easydoor.bg</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://easydoor.bg/</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>359896677878, 359896774565, 359885853333, 359889941610, 359885224330, 359889006776, 359885845750, 35934837662894</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>21768.18</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Easydoor LTD</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>office@easydoor.bg</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://easydoor.bg/</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>359896677878, 359896774565, 359885853333, 359889941610, 359885224330, 359889006776, 359885845750, 35934837662894</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>21768.18</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ECOGROUP TRANS LTD</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>lctransgeorgia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0568553808, 011502003518</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>38789.71</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>EKSEN TECHNIC SRL</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>office@eksentechnic.ro</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://eksentechnic.ro</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>40787760657, 40376856207</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>19681.83</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>EL-LOGISTIC LTD</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>lt_logistic@abv.bg</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>0725057477427, 0721955789619, 0701324008243, 0708373374976, 0718602024141</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>7233.75</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>EL-LOGISTIC LTD</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>service@nbd.ltd</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0725057477427, 0721955789619, 0701324008243, 0708373374976, 0718602024141</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>7233.75</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>EL-LOGISTIC LTD</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>consultingltd@abv.bg</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0725057477427, 0721955789619, 0701324008243, 0708373374976, 0718602024141</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7233.75</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ELAZ EOOD</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>elazeood@abv.bg</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://www.elazbg.com</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>35956843084, 359899846669, 35956843034</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>35145.7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Element Construction LLC</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>info@ec.ge</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://www.ec.ge</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>995322054262, 995322054272, 9952374737, 995533333352</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>10667.97</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ELME - EKS - MESUT MUSTAFA ET</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>info@elmeex.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://www.elmeex.com</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>359878130429, 359899556066, 359898936310</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>62051.59</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ELME - EKS - MESUT MUSTAFA ET</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>elmeex@abv.bg</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://www.elmeex.com</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>359878130429, 359899556066, 359898936310</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>62051.59</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ELME - EKS - MESUT MUSTAFA ET</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>elmeexplv@abv.bg</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.elmeex.com</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>359878130429, 359899556066, 359898936310</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>62051.59</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>info@emir.bg</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>office@emir.bg</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>marketing.sales@emir.bg</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>market.manager@emir.bg</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>account.dept@emir.bg</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>magazin1@emir.bg</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>emir.speditor@emir.bg</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>EMIR LTD</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>mehanik@emir.bg</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.emir.bg</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>35952600043, 35952607312, 35952503596, 359882122453, 359896754480, 359882122434</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>32485.58</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
           <t>RIVER MONTENEGRO D.O.O.</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Montenegro</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>montenegro.odj@gmail.com</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>38269103000, 38269218108</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
         <v>55438.33</v>
       </c>
     </row>
